--- a/extra/IHME_GBD_2019_COD_CAUSE_ICD_CODE_MAP_Y2020M10D15.XLSX
+++ b/extra/IHME_GBD_2019_COD_CAUSE_ICD_CODE_MAP_Y2020M10D15.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\DATA\IHME_RESULTS\2020_1015_GBD_2019\GBD_CAUSE_ICD_CODE_MAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DATA\recod_GC\extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4161E3A5-52E9-4F33-8425-39778E63E3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E97E4FC-E7D5-453A-AD9E-E5E20544B50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8115" yWindow="300" windowWidth="23040" windowHeight="20595" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2482,7 +2482,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2512,6 +2512,13 @@
       <name val="Times New Roman"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2578,7 +2585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2596,6 +2603,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2983,11 +2996,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -3093,10 +3106,10 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3175,10 +3188,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3251,11 +3264,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:3" ht="42" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -3445,11 +3458,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:3" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="7" t="s">
         <v>116</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -3582,7 +3595,7 @@
       </c>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>151</v>
       </c>
@@ -3604,7 +3617,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>157</v>
       </c>
@@ -4027,7 +4040,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>264</v>
       </c>
@@ -6036,7 +6049,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="281.25" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" ht="270" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>774</v>
       </c>
@@ -6047,7 +6060,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" ht="123.75" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>777</v>
       </c>
@@ -6058,7 +6071,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="315" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" ht="303.75" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>780</v>
       </c>
@@ -6069,7 +6082,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>783</v>
       </c>
@@ -6085,6 +6098,6 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>